--- a/bancos/manual/desc_fontes_de_recursos_stn.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos_stn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -412,7 +412,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Controle dos recursos não vinculados provenientes da compensação de impostos para atendimento ao disposto no artigo 9º da LC 141/2012.</t>
+          <t>Controle dos recursos não vinculados provenientes da compensação de impostos.  Essa fonte de recursos deverá ser associada ao marcador que identifica as despesas que  podem ser consideradas para cumprimento dos limites mínimos de aplicação em ASPS e em MDE.</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Royalties do Petróleo e Gás Natural Vinculados à Educação</t>
+          <t>Royalties e Participação Especial de Petróleo e Gás Natural Vinculados à Educação - Lei nº 12.858/2013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados à Educação, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial - Art. 2º da Lei nº 12.858/2013.</t>
+          <t>Controle dos recursos vinculados à Educação, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º da Lei nº 12.858/2013.</t>
         </is>
       </c>
     </row>
@@ -763,286 +763,286 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Estadual</t>
+          <t>Assistência financeira da União destinada à complementação ao pagamento dos pisos salariais para profissionais da enfermagem.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Estadual de Saúde, referentes ao Sistema Único de Saúde (SUS).</t>
+          <t>Controle dos recursos transferidos pela União, a título de assistência financeira complementar, para o cumprimento dos pisos salariais profissionais nacionais para o enfermeiro,  o técnico de enfermagem, o auxiliar de enfermagem e a parteira, conforme estabelecido pela CF/88, art. 198, §§12 a 15.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes dos Governos Municipais</t>
+          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Estadual</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências dos Fundos de Saúde de outros municípios, referentes ao Sistema Único de Saúde (SUS).</t>
+          <t>Controle dos recursos originários de transferências do Fundo Estadual de Saúde, referentes ao Sistema Único de Saúde (SUS).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transferências do Governo Federal referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes dos Governos Municipais</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências dos Fundos de Saúde de outros municípios, referentes ao Sistema Único de Saúde (SUS).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Transferências do Estado referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>Transferências do Governo Federal referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transferências de Municípios referentes a Convênios Instrumentos Congêneres vinculados à Saúde</t>
+          <t>Transferências do Estado referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros Municípios, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operações de Crédito vinculadas à Saúde</t>
+          <t>Transferências de Municípios referentes a Convênios Instrumentos Congêneres vinculados à Saúde</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros Municípios, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Royalties do Petróleo e Gás Natural vinculados à Saúde</t>
+          <t>Operações de Crédito vinculadas à Saúde</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados à Saúde, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial - Art. 2º da Lei nº 12.858/2013.</t>
+          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>Royalties e Participação Especial de Petróleo e Gás Natural vinculados à Saúde - Lei nº 12.858/2013</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de saúde.</t>
+          <t>Controle dos recursos vinculados à Saúde, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º  da Lei nº 12.858/2013.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>659</v>
+        <v>636</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Outros Recursos Vinculados à Saúde</t>
+          <t>Outras Transferências de Convênios e Instrumentos Congêneres vinculados à Saúde</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos vinculados à Saúde, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de saúde.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Transferência de Recursos do Fundo Nacional de Assistência Social - FNAS</t>
+          <t>Outros Recursos Vinculados à Saúde</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Controle os recursos originários de transferências do Fundo Nacional de Assistência Social - Lei Federal nº 8.742, 07/12/1993.</t>
+          <t>Controle dos demais recursos vinculados à Saúde, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Transferência de Recursos dos Fundos Estaduais de Assistência Social</t>
+          <t>Transferência de Recursos do Fundo Nacional de Assistência Social - FNAS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências dos fundos estaduais de assistência social.</t>
+          <t>Controle os recursos originários de transferências do Fundo Nacional de Assistência Social - Lei Federal nº 8.742, 07/12/1993.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Transferências de Recursos dos Fundos Municipais de Assistência Social</t>
+          <t>Transferência de Recursos dos Fundos Estaduais de Assistência Social</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Controle os recursos originários de transferência dos fundos municipais de assistência social.</t>
+          <t>Controle dos recursos originários de transferências dos fundos estaduais de assistência social.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transferências de Convênios e Instrumentos Congêneres vinculados à Assistência Social</t>
+          <t>Transferências de Recursos dos Fundos Municipais de Assistência Social</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada a programas da assistência social.</t>
+          <t>Controle os recursos originários de transferência dos fundos municipais de assistência social.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Outros Recursos Vinculados à Assistência Social</t>
+          <t>Transferências de Convênios e Instrumentos Congêneres vinculados à Assistência Social</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos vinculados à Assistência Social, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada a programas da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres da União</t>
+          <t>Outros Recursos Vinculados à Assistência Social</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências federais em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos demais recursos vinculados à Assistência Social, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Estados</t>
+          <t>Outras Transferências de Convênios ou Instrumentos Congêneres da União</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências estaduais em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências federais em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Municípios</t>
+          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Estados</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de municípios em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências estaduais em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres de outras Entidades</t>
+          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Municípios</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências de municípios em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Transferências da União Referentes a Compensações Financeiras pela Exploração de Recursos Naturais</t>
+          <t>Outras Transferências de Convênios ou Instrumentos Congêneres de outras Entidades</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União, originários da arrecadação de royalties do petróleo, do gás natural, da cota-parte do bônus de assinatura de contrato de partilha de produção, exceto os recursos provenientes da Lei nº 12.858/2013, destinados às áreas da saúde ou da educação.</t>
+          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
@@ -1273,374 +1273,404 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>749</v>
+        <v>720</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Outras vinculações de transferências</t>
+          <t>Transferências da União Referentes às participações na exploração de Petróleo e Gás Natural destinadas ao FEP - Lei 9.478/1997</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
+          <t>Transferências da União referentes às participações na exploração de petróleo, gás natural e outros hidrocarbonetos fluidos,  destinadas ao Fundo Especial - FEP, conforme estabelece o art. 50-F da Lei 9.478/97,  exceto os recursos obrigatórios para educação e saúde de que trata a Lei 12.858/2013.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>750</v>
+        <v>721</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Recursos da Contribuição de Intervenção no Domínio Econômico - CIDE</t>
+          <t>Transferências da União Referentes a Cessão Onerosa de Petróleo - Lei nº 13.885/2019</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
+          <t>Controle dos recursos transferidos pela União, provenientes da cessão onerosa à Petróleo Brasileiro S.A. - PETROBRAS,  do exercício das atividades de pesquisa e lavra de petróleo, gás natural e outros hidrocarbonetos fluidos,  originários dos leilões dos volumes excedentes ao limite a que se refere o § 2º do art. 1º da Lei nº 12.276,  conforme estabelecido na Lei nº 13.885/2019.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recursos da Contribuição para o Custeio do Serviço de Iluminação Pública - COSIP</t>
+          <t>Outras vinculações de transferências</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
+          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Trânsito</t>
+          <t>Recursos da Contribuição de Intervenção no Domínio Econômico - CIDE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
+          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recursos Provenientes de Taxas, Contribuições e Preços Públicos</t>
+          <t>Recursos da Contribuição para o Custeio do Serviço de Iluminação Pública - COSIP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
+          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recursos de Operações de Crédito</t>
+          <t>Recursos Vinculados ao Trânsito</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
+          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recursos de Alienação de Bens/Ativos - Administração Direta</t>
+          <t>Recursos Provenientes de Taxas, Contribuições e Preços Públicos</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recursos de Alienação de Bens/Ativos - Administração Indireta</t>
+          <t>Recursos de Operações de Crédito</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente faz parte</t>
+          <t>Recursos de Alienação de Bens/Ativos - Administração Direta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente não faz parte</t>
+          <t>Recursos de Alienação de Bens/Ativos - Administração Indireta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recursos Vinculados a Fundos</t>
+          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente faz parte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recursos de Emolumentos, Taxas e Custas</t>
+          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente não faz parte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Fundo de Combate e Erradicação da Pobreza</t>
+          <t>Recursos Vinculados a Fundos</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
+          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>799</v>
+        <v>760</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Outras Vinculações Legais</t>
+          <t>Recursos de Emolumentos, Taxas e Custas</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>800</v>
+        <v>761</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Fundo em Capitalização (Plano Previdenciário)</t>
+          <t>Recursos Vinculados ao Fundo de Combate e Erradicação da Pobreza</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Fundo em Repartição (Plano Financeiro)</t>
+          <t>Outras Vinculações Legais</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Taxa de Administração</t>
+          <t>Recursos Vinculados ao RPPS - Fundo em Capitalização (Plano Previdenciário)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
+          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Sistema de Proteção Social dos Militares (SPSM)</t>
+          <t>Recursos Vinculados ao RPPS - Fundo em Repartição (Plano Financeiro)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
+          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>860</v>
+        <v>802</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recursos Extraorçamentários Vinculados a Precatórios</t>
+          <t>Recursos Vinculados ao RPPS - Taxa de Administração</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
+          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>861</v>
+        <v>803</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recursos Extraorçamentários Vinculados a Depósitos Judiciais</t>
+          <t>Recursos Vinculados ao Sistema de Proteção Social dos Militares (SPSM)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
+          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos de Terceiros</t>
+          <t>Recursos Extraorçamentários Vinculados a Precatórios</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>869</v>
+        <v>861</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Outros Recursos Extraorçamentários</t>
+          <t>Recursos Extraorçamentários Vinculados a Depósitos Judiciais</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>880</v>
+        <v>862</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Recursos Próprios dos Consórcios</t>
+          <t>Recursos de Depósitos de Terceiros</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>898</v>
+        <v>869</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Recursos a Classificar</t>
+          <t>Outros Recursos Extraorçamentários</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
+        <v>880</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Recursos Próprios dos Consórcios</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>898</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Recursos a Classificar</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
         <v>899</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Outros Recursos Vinculados</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>Controle dos recursos cuja aplicação seja vinculada e não tenha sido enquadrado em outras especificações.</t>
         </is>

--- a/bancos/manual/desc_fontes_de_recursos_stn.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos_stn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C88"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -377,7 +377,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Recursos não Vinculados de Impostos</t>
+          <t>RECURSOS NÃO VINCULADOS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -392,7 +392,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Outros Recursos não Vinculados</t>
+          <t>OUTROS RECURSOS NÃO VINCULADOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -407,7 +407,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Recursos não vinculados da compensação de impostos.</t>
+          <t>RECURSOS NÃO VINCULADOS DA COMPENSAÇÃO DE IMPOSTOS.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -418,1259 +418,1349 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transferências do FUNDEB - Impostos e Transferências de Impostos</t>
+          <t>APOIO FINANCEIRO DA UNIÃO EM DECORRÊNCIA DE ESTADO DE CALAMIDADE PÚBLICA.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Controle dos recursos recebidos do FUNDEB referente à repartição dentro de cada Estado, com base nos incisos I, II e III do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
+          <t>Controle dos recursos transferidos pela União a título de apoio financeiro com o objetivo  de enfrentar situações de calamidade pública e suas consequências sociais e econômicas, como  o apoio financeiro decorrente da Medida Provisória n° 1.222, de 21 de maio de 2024.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transferências do FUNDEB - Complementação da União - VAAF</t>
+          <t>TRANSFERÊNCIAS DO FUNDEB - IMPOSTOS E TRANSFERÊNCIAS DE IMPOSTOS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAF, com base na alínea a do inciso V do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
+          <t>Controle dos recursos recebidos do FUNDEB referente à repartição dentro de cada Estado, com base nos incisos I, II e III do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transferências do FUNDEB - Complementação da União - VAAT</t>
+          <t>TRANSFERÊNCIAS DO FUNDEB - COMPLEMENTAÇÃO DA UNIÃO - VAAF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAT, com base na alínea b do inciso V do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
+          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAF, com base na alínea a do inciso V do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transferências do FUNDEB - Complementação da União - VAAR</t>
+          <t>TRANSFERÊNCIAS DO FUNDEB - COMPLEMENTAÇÃO DA UNIÃO - VAAT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAR, com base na alínea c, inciso V do art. 212-A da Constituição Federal.</t>
+          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAT, com base na alínea b do inciso V do art. 212-A da Constituição Federal. Na fase da despesa, quando for o caso, será necessário associar esta fonte ao marcador do percentual de aplicação no pagamento da remuneração dos profissionais da educação básica em efetivo exercício para identificar o cumprimento do percentual mínimo de 70% estabelecido no inciso XI do art. 212-A da CF.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Recursos de Precatórios do FUNDEF</t>
+          <t>TRANSFERÊNCIAS DO FUNDEB - COMPLEMENTAÇÃO DA UNIÃO - VAAR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes do recebimento de precatórios derivados de ações judiciais associadas à complementação devida pela União ao Fundo de Manutenção e Desenvolvimento do Ensino Fundamental e de Valorização do Magistério dos demais entes federados (Precatórios Fundef).</t>
+          <t>Controle dos recursos de complementação da União ao FUNDEB - VAAR, com base na alínea c, inciso V do art. 212-A da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Transferência do Salário-Educação</t>
+          <t>RECURSOS DE PRECATÓRIOS DO FUNDEF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências recebidas do Fundo Nacional do Desenvolvimento da Educação - FNDE, relativos aos repasses referentes ao salário-educação.</t>
+          <t>Controle dos recursos decorrentes do recebimento de precatórios derivados de ações judiciais associadas à complementação devida pela União ao Fundo de Manutenção e Desenvolvimento do Ensino Fundamental e de Valorização do Magistério dos demais entes federados (Precatórios Fundef).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Transferências de Recursos do FNDE referentes ao Programa Dinheiro Direto na Escola (PDDE)</t>
+          <t>RECURSOS DE PRECATÓRIOS DO FUNDEB (2007- 2020)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Dinheiro Direto na Escola (PDDE).</t>
+          <t>Controle dos recursos decorrentes do recebimento de precatórios derivados de ações  judiciais associadas aos repasses ao Fundo de Manutenção e Desenvolvimento da Educação  Básica e de Valorização dos Profissionais da Educação (Fundeb) 2007-2020, para atendimento  ao previsto no artigo 47-A da Lei nº 14.113, de 25 de dezembro de 2020.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Transferências de Recursos do FNDE referentes ao Programa Nacional de Alimentação Escolar (PNAE)</t>
+          <t>TRANSFERÊNCIA DO SALÁRIO-EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Nacional de Alimentação Escolar (PNAE).</t>
+          <t>Controle dos recursos originários de transferências recebidas do Fundo Nacional do Desenvolvimento da Educação - FNDE, relativos aos repasses referentes ao salário-educação.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Transferências de Recursos do FNDE Referentes ao Programa Nacional de Apoio ao Transporte Escolar (PNATE)</t>
+          <t>TRANSFERÊNCIAS DE RECURSOS DO FNDE REFERENTES AO PROGRAMA DINHEIRO DIRETO NA ESCOLA (PDDE)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Nacional de Apoio ao Transporte Escolar (PNATE).</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Dinheiro Direto na Escola (PDDE).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Outras Transferências de Recursos do FNDE</t>
+          <t>TRANSFERÊNCIAS DE RECURSOS DO FNDE REFERENTES AO PROGRAMA NACIONAL DE ALIMENTAÇÃO ESCOLAR (PNAE)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Nacional de Alimentação Escolar (PNAE).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Transferências do Governo Federal referentes a Convênios e Instrumentos Congêneres vinculados à Educação</t>
+          <t>TRANSFERÊNCIAS DE RECURSOS DO FNDE REFERENTES AO PROGRAMA NACIONAL DE APOIO AO TRANSPORTE ESCOLAR (PNATE)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da educação.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE, destinados ao Programa Nacional de Apoio ao Transporte Escolar (PNATE).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Transferências do Estado referentes a Convênios e Instrumentos Congêneres vinculados à Educação</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE RECURSOS DO FNDE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da educação.</t>
+          <t>Controle dos demais recursos originários de transferências do Fundo Nacional do Desenvolvimento da Educação - FNDE.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Transferências de Municípios referentes a Convênios e Instrumentos Congêneres vinculados à Educação</t>
+          <t>TRANSFERÊNCIAS DO GOVERNO FEDERAL REFERENTES A CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros municípios, cuja destinação encontra-se vinculada a programas da educação.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da educação.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Royalties e Participação Especial de Petróleo e Gás Natural Vinculados à Educação - Lei nº 12.858/2013</t>
+          <t>TRANSFERÊNCIAS DO ESTADO REFERENTES A CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados à Educação, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º da Lei nº 12.858/2013.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da educação.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operações de Crédito Vinculadas à Educação</t>
+          <t>TRANSFERÊNCIAS DE MUNICÍPIOS REFERENTES A CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da educação.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros municípios, cuja destinação encontra-se vinculada a programas da educação.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios e Instrumentos Congêneres vinculados à Educação</t>
+          <t>ROYALTIES E PARTICIPAÇÃO ESPECIAL DE PETRÓLEO E GÁS NATURAL VINCULADOS À EDUCAÇÃO - LEI Nº 12.858/2013</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de educação.</t>
+          <t>Controle dos recursos vinculados à Educação, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º da Lei nº 12.858/2013.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Transferências de Recursos dos Estados para programas de educação</t>
+          <t>OPERAÇÕES DE CRÉDITO VINCULADAS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pelos Estados para programas de educação, que não decorram de celebração de convênios, contratos de repasse e termos de parceria.</t>
+          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da educação.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Outros Recursos Vinculados à Educação</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos vinculados à Educação, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de educação.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Federal - Bloco de Manutenção das Ações e Serviços Públicos de Saúde</t>
+          <t>TRANSFERÊNCIAS DE RECURSOS DOS ESTADOS PARA PROGRAMAS DE EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS) e relacionados ao Bloco de Manutenção das Ações e Serviços Públicos de Saúde.</t>
+          <t>Controle dos recursos transferidos pelos Estados para programas de educação, que não decorram de celebração de convênios, contratos de repasse e termos de parceria.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Federal - Bloco de Estruturação da Rede de Serviços Públicos de Saúde</t>
+          <t>OUTROS RECURSOS VINCULADOS À EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS) e relacionados ao Bloco de Estruturação na Rede de Serviços Públicos de Saúde.</t>
+          <t>Controle dos demais recursos vinculados à Educação, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Federal -  Bloco de Manutenção das Ações e Serviços Públicos de Saúde -  Recursos destinados ao enfrentamento da COVID-19 no bojo da ação 21C0.</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DO GOVERNO FEDERAL - BLOCO DE MANUTENÇÃO DAS AÇÕES E SERVIÇOS PÚBLICOS DE SAÚDE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS), relacionados ao Bloco de Manutenção das Ações e Serviços Públicos de Saúde, e destinados ao enfrentamento da COVID-19 no bojo da ação 21C0 do orçamento da União.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS) e relacionados ao Bloco de Manutenção das Ações e Serviços Públicos de Saúde.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Federal -  Bloco de Estruturação da Rede de Serviços Públicos de Saúde -  Recursos destinados ao enfrentamento da COVID-19 no bojo da ação 21C0.</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DO GOVERNO FEDERAL - BLOCO DE ESTRUTURAÇÃO DA REDE DE SERVIÇOS PÚBLICOS DE SAÚDE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS), relacionados ao Bloco de Estruturação na Rede de Serviços Públicos de Saúde e destinados ao enfrentamento da COVID-19 no bojo da ação 21C0 do orçamento da União.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS) e relacionados ao Bloco de Estruturação na Rede de Serviços Públicos de Saúde.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Transferências provenientes do Governo Federal destinadas ao vencimento dos agentes comunitários de saúde e dos agentes de combate às endemias</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DO GOVERNO FEDERAL -  BLOCO DE MANUTENÇÃO DAS AÇÕES E SERVIÇOS PÚBLICOS DE SAÚDE -  RECURSOS DESTINADOS AO ENFRENTAMENTO DA COVID-19 NO BOJO DA AÇÃO 21C0.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários do Governo Federal, referentes ao Sistema Único de Saúde (SUS), relacionados ao vencimento dos agentes comunitários de saúde e dos agentes de combate às endemias, nos termos do art. 198, §7ª da Constituição Federal.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS), relacionados ao Bloco de Manutenção das Ações e Serviços Públicos de Saúde, e destinados ao enfrentamento da COVID-19 no bojo da ação 21C0 do orçamento da União.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Assistência financeira da União destinada à complementação ao pagamento dos pisos salariais para profissionais da enfermagem.</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DO GOVERNO FEDERAL -  BLOCO DE ESTRUTURAÇÃO DA REDE DE SERVIÇOS PÚBLICOS DE SAÚDE -  RECURSOS DESTINADOS AO ENFRENTAMENTO DA COVID-19 NO BOJO DA AÇÃO 21C0.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União, a título de assistência financeira complementar, para o cumprimento dos pisos salariais profissionais nacionais para o enfermeiro,  o técnico de enfermagem, o auxiliar de enfermagem e a parteira, conforme estabelecido pela CF/88, art. 198, §§12 a 15.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Nacional de Saúde, referentes ao Sistema Único de Saúde (SUS), relacionados ao Bloco de Estruturação na Rede de Serviços Públicos de Saúde e destinados ao enfrentamento da COVID-19 no bojo da ação 21C0 do orçamento da União.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes do Governo Estadual</t>
+          <t>TRANSFERÊNCIAS PROVENIENTES DO GOVERNO FEDERAL DESTINADAS AO VENCIMENTO DOS AGENTES COMUNITÁRIOS DE SAÚDE E DOS AGENTES DE COMBATE ÀS ENDEMIAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências do Fundo Estadual de Saúde, referentes ao Sistema Único de Saúde (SUS).</t>
+          <t>Controle dos recursos originários do Governo Federal, referentes ao Sistema Único de Saúde (SUS), relacionados ao vencimento dos agentes comunitários de saúde e dos agentes de combate às endemias, nos termos do art. 198, §7ª da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do SUS provenientes dos Governos Municipais</t>
+          <t>ASSISTÊNCIA FINANCEIRA DA UNIÃO DESTINADA À COMPLEMENTAÇÃO AO PAGAMENTO DOS PISOS SALARIAIS PARA PROFISSIONAIS DA ENFERMAGEM.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências dos Fundos de Saúde de outros municípios, referentes ao Sistema Único de Saúde (SUS).</t>
+          <t>Controle dos recursos transferidos pela União, a título de assistência financeira complementar, para o cumprimento dos pisos salariais profissionais nacionais para o enfermeiro,  o técnico de enfermagem, o auxiliar de enfermagem e a parteira, conforme estabelecido pela CF/88, art. 198, §§12 a 15.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Transferências do Governo Federal referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DO GOVERNO ESTADUAL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências do Fundo Estadual de Saúde, referentes ao Sistema Único de Saúde (SUS).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transferências do Estado referentes a Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO SUS PROVENIENTES DOS GOVERNOS MUNICIPAIS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências dos Fundos de Saúde de outros municípios, referentes ao Sistema Único de Saúde (SUS).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Transferências de Municípios referentes a Convênios Instrumentos Congêneres vinculados à Saúde</t>
+          <t>TRANSFERÊNCIAS DO GOVERNO FEDERAL REFERENTES A CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À SAÚDE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros Municípios, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com a União, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operações de Crédito vinculadas à Saúde</t>
+          <t>TRANSFERÊNCIAS DO ESTADO REFERENTES A CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À SAÚDE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da saúde.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com os Estados, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Royalties e Participação Especial de Petróleo e Gás Natural vinculados à Saúde - Lei nº 12.858/2013</t>
+          <t>TRANSFERÊNCIAS DE MUNICÍPIOS REFERENTES A CONVÊNIOS INSTRUMENTOS CONGÊNERES VINCULADOS À SAÚDE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados à Saúde, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º  da Lei nº 12.858/2013.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres com outros Municípios, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios e Instrumentos Congêneres vinculados à Saúde</t>
+          <t>OPERAÇÕES DE CRÉDITO VINCULADAS À SAÚDE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de saúde.</t>
+          <t>Controle dos recursos originários de operações de crédito, cuja destinação encontra-se vinculada a programas da saúde.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Outros Recursos Vinculados à Saúde</t>
+          <t>ROYALTIES E PARTICIPAÇÃO ESPECIAL DE PETRÓLEO E GÁS NATURAL VINCULADOS À SAÚDE - LEI Nº 12.858/2013</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos vinculados à Saúde, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos vinculados à Saúde, originários de transferências recebidas pelos entes, relativos a Royalties e Participação Especial com base no art. 2º  da Lei nº 12.858/2013.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38">
-        <v>660</v>
+        <v>636</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Transferência de Recursos do Fundo Nacional de Assistência Social - FNAS</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À SAÚDE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Controle os recursos originários de transferências do Fundo Nacional de Assistência Social - Lei Federal nº 8.742, 07/12/1993.</t>
+          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada a programas de saúde.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Transferência de Recursos dos Fundos Estaduais de Assistência Social</t>
+          <t>OUTROS RECURSOS VINCULADOS À SAÚDE</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências dos fundos estaduais de assistência social.</t>
+          <t>Controle dos demais recursos vinculados à Saúde, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Transferências de Recursos dos Fundos Municipais de Assistência Social</t>
+          <t>TRANSFERÊNCIA DE RECURSOS DO FUNDO NACIONAL DE ASSISTÊNCIA SOCIAL - FNAS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Controle os recursos originários de transferência dos fundos municipais de assistência social.</t>
+          <t>Controle os recursos originários de transferências do Fundo Nacional de Assistência Social - Lei Federal nº 8.742, 07/12/1993.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Transferências de Convênios e Instrumentos Congêneres vinculados à Assistência Social</t>
+          <t>TRANSFERÊNCIA DE RECURSOS DOS FUNDOS ESTADUAIS DE ASSISTÊNCIA SOCIAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada a programas da assistência social.</t>
+          <t>Controle dos recursos originários de transferências dos fundos estaduais de assistência social.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42">
-        <v>669</v>
+        <v>662</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Outros Recursos Vinculados à Assistência Social</t>
+          <t>TRANSFERÊNCIAS DE RECURSOS DOS FUNDOS MUNICIPAIS DE ASSISTÊNCIA SOCIAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos vinculados à Assistência Social, não enquadrados nas especificações anteriores.</t>
+          <t>Controle os recursos originários de transferência dos fundos municipais de assistência social.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43">
-        <v>700</v>
+        <v>665</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres da União</t>
+          <t>TRANSFERÊNCIAS DE CONVÊNIOS E INSTRUMENTOS CONGÊNERES VINCULADOS À ASSISTÊNCIA SOCIAL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências federais em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada a programas da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44">
-        <v>701</v>
+        <v>669</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Estados</t>
+          <t>OUTROS RECURSOS VINCULADOS À ASSISTÊNCIA SOCIAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências estaduais em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos demais recursos vinculados à Assistência Social, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres dos Municípios</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS OU INSTRUMENTOS CONGÊNERES DA UNIÃO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de municípios em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências federais em decorrência da celebração de convênios e instrumentos congêneres cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Outras Transferências de Convênios ou Instrumentos Congêneres de outras Entidades</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS OU INSTRUMENTOS CONGÊNERES DOS ESTADOS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
+          <t>Controle dos recursos originários de transferências estaduais em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Transferências dos Estados Referentes a Compensações Financeiras pela Exploração de Recursos Naturais</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS OU INSTRUMENTOS CONGÊNERES DOS MUNICÍPIOS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pelos Estados, originários da arrecadação de royalties do petróleo, do gás natural, da cota-parte do bônus de assinatura de contrato de partilha de produção.</t>
+          <t>Controle dos recursos originários de transferências de municípios em decorrência da celebração de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Transferência Especial da União</t>
+          <t>OUTRAS TRANSFERÊNCIAS DE CONVÊNIOS OU INSTRUMENTOS CONGÊNERES DE OUTRAS ENTIDADES</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União provenientes de emendas individuais impositivas ao orçamento da União, por meio de transferências especiais, nos termos do art. 166-A da Constituição Federal.</t>
+          <t>Controle dos recursos originários de transferências de entidades privadas, estrangeiras ou multigovernamentais em virtude de assinatura de convênios e instrumentos congêneres, cuja destinação encontra-se vinculada aos seus objetos. Não serão controlados por esta fonte os recursos de convênios ou contratos de repasse vinculados a programas da educação, da saúde e da assistência social.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Transferências da União - inciso I do art. 5º da Lei Complementar 173/2020</t>
+          <t>TRANSFERÊNCIAS DA UNIÃO REFERENTES A COMPENSAÇÕES FINANCEIRAS PELA EXPLORAÇÃO DE RECURSOS NATURAIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Controle dos recursos provenientes de transferência da União com base no disposto no inciso I do art. 5º da Lei Complementar 173, de 27 de maio de 2020.</t>
+          <t>Controle dos recursos transferidos pela União, originários da arrecadação de royalties do petróleo, do gás natural, da cota-parte do bônus de assinatura de contrato de partilha de produção, exceto os recursos provenientes da Lei nº 12.858/2013, destinados às áreas da saúde ou da educação.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Transferência da União Referente à Compensação Financeira de Recursos Minerais</t>
+          <t>TRANSFERÊNCIAS DOS ESTADOS REFERENTES A COMPENSAÇÕES FINANCEIRAS PELA EXPLORAÇÃO DE RECURSOS NATURAIS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União, referentes à compensação financeira pela exploração de recursos minerais em atendimento às destinações e vedações previstas na legislação.</t>
+          <t>Controle dos recursos transferidos pelos Estados, originários da arrecadação de royalties do petróleo, do gás natural, da cota-parte do bônus de assinatura de contrato de partilha de produção.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Transferência da União referente à Compensação Financeira de Recursos Hídricos</t>
+          <t>TRANSFERÊNCIA ESPECIAL DA UNIÃO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União, referentes à compensação financeira de recursos hídricos em atendimento às destinações e vedações previstas na legislação.</t>
+          <t>Controle dos recursos transferidos pela União provenientes de emendas individuais impositivas ao orçamento da União, por meio de transferências especiais, nos termos do art. 166-A da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Transferência Especial dos Estados</t>
+          <t>TRANSFERÊNCIAS DA UNIÃO - INCISO I DO ART. 5º DA LEI COMPLEMENTAR 173/2020</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pelos Estados provenientes de emendas individuais impositivas ao orçamento desses entes, por meio de transferências especiais, nos termos das constituições estaduais que reproduziram o disposto no art. 166-A da Constituição Federal.</t>
+          <t>Controle dos recursos provenientes de transferência da União com base no disposto no inciso I do art. 5º da Lei Complementar 173, de 27 de maio de 2020.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Demais Transferências Obrigatórias não Decorrentes de Repartições de Receitas.</t>
+          <t>TRANSFERÊNCIA DA UNIÃO REFERENTE À COMPENSAÇÃO FINANCEIRA DE RECURSOS MINERAIS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Controla os recursos originários de transferências obrigatórias da União que não decorram de repartição de receitas, como as transferências a título de auxílio ou apoio financeiro, e para os quais não tenha sido criada fonte ou destinação de receitas específica.</t>
+          <t>Controle dos recursos transferidos pela União, referentes à compensação financeira pela exploração de recursos minerais em atendimento às destinações e vedações previstas na legislação.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do Fundo Penitenciário - FUNPEN</t>
+          <t>TRANSFERÊNCIA DA UNIÃO REFERENTE À COMPENSAÇÃO FINANCEIRA DE RECURSOS HÍDRICOS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Controla as transferências obrigatórias de recursos do Fundo Penitenciário Nacional - FUNPEN.</t>
+          <t>Controle dos recursos transferidos pela União, referentes à compensação financeira de recursos hídricos em atendimento às destinações e vedações previstas na legislação.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do Fundo de Segurança Pública - FSP</t>
+          <t>TRANSFERÊNCIA ESPECIAL DOS ESTADOS</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Controla as transferências obrigatórias de recursos do Fundo de Segurança Pública - FSP</t>
+          <t>Controle dos recursos transferidos pelos Estados provenientes de emendas individuais impositivas ao orçamento desses entes, por meio de transferências especiais, nos termos das constituições estaduais que reproduziram o disposto no art. 166-A da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Transferências Fundo a Fundo de Recursos do Fundo de Amparo ao Trabalhador - FAT</t>
+          <t>DEMAIS TRANSFERÊNCIAS OBRIGATÓRIAS NÃO DECORRENTES DE REPARTIÇÕES DE RECEITAS.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Controla as transferências obrigatórias de recursos do Fundo de Amparo ao Trabalhador - FAT</t>
+          <t>Controla os recursos originários de transferências obrigatórias da União que não decorram de repartição de receitas, como as transferências a título de auxílio ou apoio financeiro, e para os quais não tenha sido criada fonte ou destinação de receitas específica.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Transferências Destinadas ao Setor Cultural - LC nº 195/2022 - Art. 5º - Audiovisual</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO FUNDO PENITENCIÁRIO - FUNPEN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Controla a parcela dos recursos provenientes das transferências efetuadas pela União destinadas ao setor cultural, especificamente ao setor audiovisual, como ação emergencial adotada em decorrência dos efeitos econômicos e sociais da pandemia da covid-19, em cumprimento ao Art. 5º da Lei Complementar nº 195, de 8 de julho de 2022.</t>
+          <t>Controla as transferências obrigatórias de recursos do Fundo Penitenciário Nacional - FUNPEN.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Transferências Destinadas ao Setor cultural - LC nº 195/2022 - Art. 8º - Demais Setores da Cultura</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO FUNDO DE SEGURANÇA PÚBLICA - FSP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Controla a parcela dos recursos provenientes das transferências efetuadas pela União destinadas ao setor cultural, como ação emergencial adotada em decorrência dos efeitos econômicos e sociais da pandemia da covid-19, em cumprimento ao Art. 8º da Lei Complementar nº 195, de 8 de julho de 2022</t>
+          <t>Controla as transferências obrigatórias de recursos do Fundo de Segurança Pública - FSP</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Assistência Financeira Transporte Coletivo - Art. 5º, Inciso IV, EC nº 123/2022</t>
+          <t>TRANSFERÊNCIAS FUNDO A FUNDO DE RECURSOS DO FUNDO DE AMPARO AO TRABALHADOR - FAT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Controla os recursos provenientes das transferências da União a título de assistência financeira a serem utilizados no custeio da garantia prevista no §2º do art. 230 da CF, de gratuidade dos transportes coletivos urbanos aos maiores de 65 anos, conforme prevê o inciso IV, art. 5º, da Emenda Constitucional nº 123/2022.</t>
+          <t>Controla as transferências obrigatórias de recursos do Fundo de Amparo ao Trabalhador - FAT</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Auxílio Financeiro - Outorga Crédito Tributário ICMS - Art. 5º, Inciso V, EC nº 123/2022</t>
+          <t>TRANSFERÊNCIAS DESTINADAS AO SETOR CULTURAL - LC Nº 195/2022 - ART. 5º - AUDIOVISUAL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Controla os recursos provenientes das transferências da União a título de auxílio financeiro para os Estados e o Distrito Federal que outorgarem créditos tributários do Imposto sobre Operações relativas à Circulação de Mercadorias e sobre Prestações de Serviços de Transporte Interestadual e Intermunicipal e de Comunicação (ICMS) aos produtores ou distribuidores de etanol hidratado em seu território, em montante equivalente ao valor recebido, conforme prevê o Inciso V, art. 5º, da Emenda Constitucional nº 123/2022.</t>
+          <t>Controla a parcela dos recursos provenientes das transferências efetuadas pela União destinadas ao setor cultural, especificamente ao setor audiovisual, como ação emergencial adotada em decorrência dos efeitos econômicos e sociais da pandemia da covid-19, em cumprimento ao Art. 5º da Lei Complementar nº 195, de 8 de julho de 2022.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Transferências da Política Nacional Aldir Blanc de Fomento à Cultura - Lei nº 14.399/2022</t>
+          <t>TRANSFERÊNCIAS DESTINADAS AO SETOR CULTURAL - LC Nº 195/2022 - ART. 8º - DEMAIS SETORES DA CULTURA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Controla os recursos provenientes de transferências efetuadas pela União em decorrência da Política Nacional Aldir Blanc de Fomento à Cultura previstas no art. 6º da Lei nº 14.399, de 8 de julho de 2022.</t>
+          <t>Controla a parcela dos recursos provenientes das transferências efetuadas pela União destinadas ao setor cultural, como ação emergencial adotada em decorrência dos efeitos econômicos e sociais da pandemia da covid-19, em cumprimento ao Art. 8º da Lei Complementar nº 195, de 8 de julho de 2022</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Transferências da União Referentes às participações na exploração de Petróleo e Gás Natural destinadas ao FEP - Lei 9.478/1997</t>
+          <t>ASSISTÊNCIA FINANCEIRA TRANSPORTE COLETIVO - ART. 5º, INCISO IV, EC Nº 123/2022</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Transferências da União referentes às participações na exploração de petróleo, gás natural e outros hidrocarbonetos fluidos,  destinadas ao Fundo Especial - FEP, conforme estabelece o art. 50-F da Lei 9.478/97,  exceto os recursos obrigatórios para educação e saúde de que trata a Lei 12.858/2013.</t>
+          <t>Controla os recursos provenientes das transferências da União a título de assistência financeira a serem utilizados no custeio da garantia prevista no §2º do art. 230 da CF, de gratuidade dos transportes coletivos urbanos aos maiores de 65 anos, conforme prevê o inciso IV, art. 5º, da Emenda Constitucional nº 123/2022.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Transferências da União Referentes a Cessão Onerosa de Petróleo - Lei nº 13.885/2019</t>
+          <t>AUXÍLIO FINANCEIRO - OUTORGA CRÉDITO TRIBUTÁRIO ICMS - ART. 5º, INCISO V, EC Nº 123/2022</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Controle dos recursos transferidos pela União, provenientes da cessão onerosa à Petróleo Brasileiro S.A. - PETROBRAS,  do exercício das atividades de pesquisa e lavra de petróleo, gás natural e outros hidrocarbonetos fluidos,  originários dos leilões dos volumes excedentes ao limite a que se refere o § 2º do art. 1º da Lei nº 12.276,  conforme estabelecido na Lei nº 13.885/2019.</t>
+          <t>Controla os recursos provenientes das transferências da União a título de auxílio financeiro para os Estados e o Distrito Federal que outorgarem créditos tributários do Imposto sobre Operações relativas à Circulação de Mercadorias e sobre Prestações de Serviços de Transporte Interestadual e Intermunicipal e de Comunicação (ICMS) aos produtores ou distribuidores de etanol hidratado em seu território, em montante equivalente ao valor recebido, conforme prevê o Inciso V, art. 5º, da Emenda Constitucional nº 123/2022.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64">
-        <v>749</v>
+        <v>719</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Outras vinculações de transferências</t>
+          <t>TRANSFERÊNCIAS DA POLÍTICA NACIONAL ALDIR BLANC DE FOMENTO À CULTURA - LEI Nº 14.399/2022</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
+          <t>Controla os recursos provenientes de transferências efetuadas pela União em decorrência da Política Nacional Aldir Blanc de Fomento à Cultura previstas no art. 6º da Lei nº 14.399, de 8 de julho de 2022.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Recursos da Contribuição de Intervenção no Domínio Econômico - CIDE</t>
+          <t>TRANSFERÊNCIAS DA UNIÃO REFERENTES ÀS PARTICIPAÇÕES NA EXPLORAÇÃO DE PETRÓLEO E GÁS NATURAL DESTINADAS AO FEP - LEI 9.478/1997</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
+          <t>Transferências da União referentes às participações na exploração de petróleo, gás natural e outros hidrocarbonetos fluidos,  destinadas ao Fundo Especial - FEP, conforme estabelece o art. 50-F da Lei 9.478/97,  exceto os recursos obrigatórios para educação e saúde de que trata a Lei 12.858/2013.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66">
-        <v>751</v>
+        <v>721</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Recursos da Contribuição para o Custeio do Serviço de Iluminação Pública - COSIP</t>
+          <t>TRANSFERÊNCIAS DA UNIÃO REFERENTES A CESSÃO ONEROSA DE PETRÓLEO - LEI Nº 13.885/2019</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
+          <t>Controle dos recursos transferidos pela União, provenientes da cessão onerosa à Petróleo Brasileiro S.A. - PETROBRAS,  do exercício das atividades de pesquisa e lavra de petróleo, gás natural e outros hidrocarbonetos fluidos,  originários dos leilões dos volumes excedentes ao limite a que se refere o § 2º do art. 1º da Lei nº 12.276,  conforme estabelecido na Lei nº 13.885/2019.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Trânsito</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DA UNIÃO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
+          <t>Controle dos recursos de outras transferências vinculadas da União, não enquadrados nas  especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Recursos Provenientes de Taxas, Contribuições e Preços Públicos</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DOS ESTADOS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
+          <t>Controle dos recursos de outras transferências vinculadas dos Estados, não enquadrados nas  especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recursos de Operações de Crédito</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
+          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Recursos de Alienação de Bens/Ativos - Administração Direta</t>
+          <t>RECURSOS DA CONTRIBUIÇÃO DE INTERVENÇÃO NO DOMÍNIO ECONÔMICO - CIDE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recursos de Alienação de Bens/Ativos - Administração Indireta</t>
+          <t>RECURSOS DA CONTRIBUIÇÃO PARA O CUSTEIO DO SERVIÇO DE ILUMINAÇÃO PÚBLICA - COSIP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente faz parte</t>
+          <t>RECURSOS VINCULADOS AO TRÂNSITO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos Judiciais - Lides das quais o Ente não faz parte</t>
+          <t>RECURSOS PROVENIENTES DE TAXAS, CONTRIBUIÇÕES E PREÇOS PÚBLICOS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Recursos Vinculados a Fundos</t>
+          <t>RECURSOS DE OPERAÇÕES DE CRÉDITO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
+          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recursos de Emolumentos, Taxas e Custas</t>
+          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO DIRETA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Fundo de Combate e Erradicação da Pobreza</t>
+          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO INDIRETA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>799</v>
+        <v>757</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Outras Vinculações Legais</t>
+          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE FAZ PARTE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>800</v>
+        <v>758</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Fundo em Capitalização (Plano Previdenciário)</t>
+          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE NÃO FAZ PARTE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>801</v>
+        <v>759</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Fundo em Repartição (Plano Financeiro)</t>
+          <t>RECURSOS VINCULADOS A FUNDOS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>802</v>
+        <v>760</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao RPPS - Taxa de Administração</t>
+          <t>RECURSOS DE EMOLUMENTOS, TAXAS E CUSTAS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
+          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>803</v>
+        <v>761</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Recursos Vinculados ao Sistema de Proteção Social dos Militares (SPSM)</t>
+          <t>RECURSOS VINCULADOS AO FUNDO DE COMBATE E ERRADICAÇÃO DA POBREZA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
+          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>860</v>
+        <v>799</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Recursos Extraorçamentários Vinculados a Precatórios</t>
+          <t>OUTRAS VINCULAÇÕES LEGAIS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
+          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>861</v>
+        <v>800</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Recursos Extraorçamentários Vinculados a Depósitos Judiciais</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM CAPITALIZAÇÃO (PLANO PREVIDENCIÁRIO)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
+          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>862</v>
+        <v>801</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Recursos de Depósitos de Terceiros</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM REPARTIÇÃO (PLANO FINANCEIRO)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
+          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>869</v>
+        <v>802</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Outros Recursos Extraorçamentários</t>
+          <t>RECURSOS VINCULADOS AO RPPS - TAXA DE ADMINISTRAÇÃO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
+          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>880</v>
+        <v>803</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Recursos Próprios dos Consórcios</t>
+          <t>RECURSOS VINCULADOS AO SISTEMA DE PROTEÇÃO SOCIAL DOS MILITARES (SPSM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>898</v>
+        <v>804</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recursos a Classificar</t>
+          <t>DEMAIS RECURSOS PREVIDENCIÁRIOS</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+          <t>Controle de demais recursos vinculados a benefícios previdenciários, como os benefícios  mantidos sob responsabilidade financeira direta do Tesouro do ente Federativo, concedidos  em atendimento a legislações específicas e que não foram incorporados ao RPPS.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88">
+        <v>860</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A PRECATÓRIOS</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>861</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A DEPÓSITOS JUDICIAIS</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>862</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>RECURSOS DE DEPÓSITOS DE TERCEIROS</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>869</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OUTROS RECURSOS EXTRAORÇAMENTÁRIOS</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>880</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>RECURSOS PRÓPRIOS DOS CONSÓRCIOS</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>898</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>RECURSOS A CLASSIFICAR</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
         <v>899</v>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Outros Recursos Vinculados</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>OUTROS RECURSOS VINCULADOS</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>Controle dos recursos cuja aplicação seja vinculada e não tenha sido enquadrado em outras especificações.</t>
         </is>

--- a/bancos/manual/desc_fontes_de_recursos_stn.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos_stn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C94"/>
+  <dimension ref="A1:C95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1348,419 +1348,434 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>747</v>
+        <v>722</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DA UNIÃO</t>
+          <t>TRANSFERÊNCIAS DO FUNDO DE EQUALIZAÇÃO FEDERATIVA (FEF) - LC Nº 212/2025 - PROPAG</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Controle dos recursos de outras transferências vinculadas da União, não enquadrados nas  especificações anteriores.</t>
+          <t>Controla os recursos recebidos pelos Estados provenientes das transferências do FEF,  em observância ao disposto no art. 9º, §2º da Lei Complementar nº 212, de 13 de janeiro  de 2025.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DOS ESTADOS</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DA UNIÃO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Controle dos recursos de outras transferências vinculadas dos Estados, não enquadrados nas  especificações anteriores.</t>
+          <t>Controle dos recursos de outras transferências vinculadas da União, não enquadrados nas  especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS DOS ESTADOS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos de outras transferências vinculadas dos Estados, não enquadrados nas  especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>RECURSOS DA CONTRIBUIÇÃO DE INTERVENÇÃO NO DOMÍNIO ECONÔMICO - CIDE</t>
+          <t>OUTRAS VINCULAÇÕES DE TRANSFERÊNCIAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
+          <t>Controle dos recursos de outras transferências vinculadas, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RECURSOS DA CONTRIBUIÇÃO PARA O CUSTEIO DO SERVIÇO DE ILUMINAÇÃO PÚBLICA - COSIP</t>
+          <t>RECURSOS DA CONTRIBUIÇÃO DE INTERVENÇÃO NO DOMÍNIO ECONÔMICO - CIDE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
+          <t>Controle dos recursos recebidos pelos Estados, Distrito Federal e Municípios, decorrentes da distribuição da arrecadação da União com a CIDE - Combustíveis, com base no disposto na Lei nº 10.336/2001.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO TRÂNSITO</t>
+          <t>RECURSOS DA CONTRIBUIÇÃO PARA O CUSTEIO DO SERVIÇO DE ILUMINAÇÃO PÚBLICA - COSIP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
+          <t>Controle dos recursos da COSIP, nos termos do artigo 149-A da Constituição Federal da República.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>RECURSOS PROVENIENTES DE TAXAS, CONTRIBUIÇÕES E PREÇOS PÚBLICOS</t>
+          <t>RECURSOS VINCULADOS AO TRÂNSITO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
+          <t>Controle dos recursos com a cobrança das multas de trânsito nos termos do art. 320 da Lei nº 9.503/1997 - Código de Trânsito Brasileiro.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RECURSOS DE OPERAÇÕES DE CRÉDITO</t>
+          <t>RECURSOS PROVENIENTES DE TAXAS, CONTRIBUIÇÕES E PREÇOS PÚBLICOS</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
+          <t>Controle dos recursos de taxas, contribuições e preços públicos vinculados conforme legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO DIRETA</t>
+          <t>RECURSOS DE OPERAÇÕES DE CRÉDITO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos originários de operações de crédito, exceto as operações cuja aplicação esteja destinada a programas de educação e saúde.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO INDIRETA</t>
+          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO DIRETA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Direta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE FAZ PARTE</t>
+          <t>RECURSOS DE ALIENAÇÃO DE BENS/ATIVOS - ADMINISTRAÇÃO INDIRETA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos decorrentes da alienação de bens da Administração Indireta, nos termos do art. 44 da Lei Complementar nº 101/2000.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE NÃO FAZ PARTE</t>
+          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE FAZ PARTE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente faz parte, com base na Lei Complementar nº 151/2015, no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS A FUNDOS</t>
+          <t>RECURSOS DE DEPÓSITOS JUDICIAIS - LIDES DAS QUAIS O ENTE NÃO FAZ PARTE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
+          <t>Controle dos recursos de depósitos judiciais apropriados pelo ente de lides das quais o ente não faz parte, com base no art. 101 do ADCT da Constituição Federal.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RECURSOS DE EMOLUMENTOS, TAXAS E CUSTAS</t>
+          <t>RECURSOS VINCULADOS A FUNDOS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
+          <t>Controle dos recursos vinculados a fundos, com exceção dos fundos relacionados à saúde, à educação, à assistência social e aos regimes de previdência.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO FUNDO DE COMBATE E ERRADICAÇÃO DA POBREZA</t>
+          <t>RECURSOS DE EMOLUMENTOS, TAXAS E CUSTAS</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
+          <t>Controle dos recursos de emolumentos, taxas e outros recursos arrecadados, judiciais ou extrajudiciais, observado o disposto em legislações específicas.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82">
-        <v>799</v>
+        <v>761</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>OUTRAS VINCULAÇÕES LEGAIS</t>
+          <t>RECURSOS VINCULADOS AO FUNDO DE COMBATE E ERRADICAÇÃO DA POBREZA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
+          <t>Controle dos recursos vinculados ao Fundo de Combate e Erradicação da Pobreza, na forma prevista nos art. 82 do ADCT e da Lei Complementar nº 111, de 6 de julho de 2001.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM CAPITALIZAÇÃO (PLANO PREVIDENCIÁRIO)</t>
+          <t>OUTRAS VINCULAÇÕES LEGAIS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM REPARTIÇÃO (PLANO FINANCEIRO)</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM CAPITALIZAÇÃO (PLANO PREVIDENCIÁRIO)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - TAXA DE ADMINISTRAÇÃO</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM REPARTIÇÃO (PLANO FINANCEIRO)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
+          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO SISTEMA DE PROTEÇÃO SOCIAL DOS MILITARES (SPSM)</t>
+          <t>RECURSOS VINCULADOS AO RPPS - TAXA DE ADMINISTRAÇÃO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
+          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DEMAIS RECURSOS PREVIDENCIÁRIOS</t>
+          <t>RECURSOS VINCULADOS AO SISTEMA DE PROTEÇÃO SOCIAL DOS MILITARES (SPSM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Controle de demais recursos vinculados a benefícios previdenciários, como os benefícios  mantidos sob responsabilidade financeira direta do Tesouro do ente Federativo, concedidos  em atendimento a legislações específicas e que não foram incorporados ao RPPS.</t>
+          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A PRECATÓRIOS</t>
+          <t>DEMAIS RECURSOS PREVIDENCIÁRIOS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
+          <t>Controle de demais recursos vinculados a benefícios previdenciários, como os benefícios  mantidos sob responsabilidade financeira direta do Tesouro do ente Federativo, concedidos  em atendimento a legislações específicas e que não foram incorporados ao RPPS.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A DEPÓSITOS JUDICIAIS</t>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A PRECATÓRIOS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RECURSOS DE DEPÓSITOS DE TERCEIROS</t>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A DEPÓSITOS JUDICIAIS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OUTROS RECURSOS EXTRAORÇAMENTÁRIOS</t>
+          <t>RECURSOS DE DEPÓSITOS DE TERCEIROS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
+          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS DOS CONSÓRCIOS</t>
+          <t>OUTROS RECURSOS EXTRAORÇAMENTÁRIOS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>898</v>
+        <v>880</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RECURSOS A CLASSIFICAR</t>
+          <t>RECURSOS PRÓPRIOS DOS CONSÓRCIOS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94">
+        <v>898</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RECURSOS A CLASSIFICAR</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
         <v>899</v>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t>OUTROS RECURSOS VINCULADOS</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>Controle dos recursos cuja aplicação seja vinculada e não tenha sido enquadrado em outras especificações.</t>
         </is>

--- a/bancos/manual/desc_fontes_de_recursos_stn.xlsx
+++ b/bancos/manual/desc_fontes_de_recursos_stn.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C95"/>
+  <dimension ref="A1:C96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1588,194 +1588,209 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>799</v>
+        <v>763</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>OUTRAS VINCULAÇÕES LEGAIS</t>
+          <t>RECURSOS PRÓPRIOS DOS ESTADOS VINCULADOS AO PROPAG - LC Nº 212/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
+          <t>Controla os recursos próprios dos estados relativos ao percentual do saldo devedor atualizado das dívidas elencadas no art. 2º, § 1º, da Lei Complementar nº 212, de 13 de janeiro de 2025, e respectivos rendimentos, que o estado se comprometeu a aplicar diretamente nas finalidades previstas no art. 5º, § 2º, da referida Lei Complementar, conforme inciso I e III do art. 65 do Decreto nº12.433, de 14 de abril de 2025. FR a ser utilizada quando o estado optar pela contabilização dos recursos do art. 65 do Decreto nº 12.433/2025 por meio de fundo público específico.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM CAPITALIZAÇÃO (PLANO PREVIDENCIÁRIO)</t>
+          <t>OUTRAS VINCULAÇÕES LEGAIS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle de outros recursos vinculados por lei, não enquadrados nas especificações anteriores.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM REPARTIÇÃO (PLANO FINANCEIRO)</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM CAPITALIZAÇÃO (PLANO PREVIDENCIÁRIO)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
+          <t>Controle dos recursos vinculados ao fundo em capitalização do RPPS. Esse plano existe tanto nos entes que segregaram quanto nos que não segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase das despesas, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO RPPS - TAXA DE ADMINISTRAÇÃO</t>
+          <t>RECURSOS VINCULADOS AO RPPS - FUNDO EM REPARTIÇÃO (PLANO FINANCEIRO)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
+          <t>Controle dos recursos vinculados ao fundo em repartição do RPPS. Esse plano deve existir somente nos entes que segregaram a massa dos segurados, observando-se o disposto na Portaria MF nº 464/2018. Na fase da despesa, será necessário associar esta fonte ao marcador que identifica a qual Poder ou Órgão se refere a despesa quando ela é executada no PO RPPS.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RECURSOS VINCULADOS AO SISTEMA DE PROTEÇÃO SOCIAL DOS MILITARES (SPSM)</t>
+          <t>RECURSOS VINCULADOS AO RPPS - TAXA DE ADMINISTRAÇÃO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
+          <t>Controle dos recursos destinados ao custeio das despesas necessárias à organização e ao funcionamento da unidade gestora do RPPS, observando-se o disposto na Portaria MPS nº 402/2008 e na Portaria MF nº 464/2018, ambas alteradas pela Portaria ME nº 19.451/2020.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>DEMAIS RECURSOS PREVIDENCIÁRIOS</t>
+          <t>RECURSOS VINCULADOS AO SISTEMA DE PROTEÇÃO SOCIAL DOS MILITARES (SPSM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Controle de demais recursos vinculados a benefícios previdenciários, como os benefícios  mantidos sob responsabilidade financeira direta do Tesouro do ente Federativo, concedidos  em atendimento a legislações específicas e que não foram incorporados ao RPPS.</t>
+          <t>Controle dos recursos vinculados ao Sistema de Proteção Social dos Militares (SPSM), com base na Lei nº 6.880/1980 (Estatuto dos Militares), alterada pela Lei nº 13.954/2019.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89">
-        <v>860</v>
+        <v>804</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A PRECATÓRIOS</t>
+          <t>DEMAIS RECURSOS PREVIDENCIÁRIOS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
+          <t>Controle de demais recursos vinculados a benefícios previdenciários, como os benefícios  mantidos sob responsabilidade financeira direta do Tesouro do ente Federativo, concedidos  em atendimento a legislações específicas e que não foram incorporados ao RPPS.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A DEPÓSITOS JUDICIAIS</t>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A PRECATÓRIOS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados ao pagamento de precatórios.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RECURSOS DE DEPÓSITOS DE TERCEIROS</t>
+          <t>RECURSOS EXTRAORÇAMENTÁRIOS VINCULADOS A DEPÓSITOS JUDICIAIS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
+          <t>Controle dos recursos financeiros junto aos tribunais de justiça vinculados aos depósitos judiciais.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92">
-        <v>869</v>
+        <v>862</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OUTROS RECURSOS EXTRAORÇAMENTÁRIOS</t>
+          <t>RECURSOS DE DEPÓSITOS DE TERCEIROS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
+          <t>Controle dos recursos financeiros decorrentes de depósitos de terceiros.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93">
-        <v>880</v>
+        <v>869</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RECURSOS PRÓPRIOS DOS CONSÓRCIOS</t>
+          <t>OUTROS RECURSOS EXTRAORÇAMENTÁRIOS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
+          <t>Controle dos demais recursos financeiros extraorçamentários, como, por exemplo, retenções e consignações.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94">
-        <v>898</v>
+        <v>880</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RECURSOS A CLASSIFICAR</t>
+          <t>RECURSOS PRÓPRIOS DOS CONSÓRCIOS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+          <t>Controle dos recursos próprios dos Consórcios Públicos (utilizada pelos consórcios públicos)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95">
+        <v>898</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>RECURSOS A CLASSIFICAR</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Classificação temporária enquanto não se identifica a correta vinculação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
         <v>899</v>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B96" t="inlineStr">
         <is>
           <t>OUTROS RECURSOS VINCULADOS</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>Controle dos recursos cuja aplicação seja vinculada e não tenha sido enquadrado em outras especificações.</t>
         </is>
